--- a/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/application_inventory.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/application_inventory.xlsx
@@ -503,12 +503,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salesforce Core 0</t>
+          <t>Kyriba Instance 0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,20 +518,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.64</v>
+        <v>3.92</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -543,35 +543,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ServiceNow Module 1</t>
+          <t>Salesforce Core 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP ECC Module 2</t>
+          <t>ServiceNow Module 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -598,16 +598,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.99</v>
+        <v>2.01</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 3</t>
+          <t>SAP ECC Module 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -643,11 +643,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.66</v>
+        <v>2.99</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 4</t>
+          <t>Custom .NET Instance 4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -678,20 +678,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -703,17 +703,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ServiceNow Instance 5</t>
+          <t>S/4HANA Instance 5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.85</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -743,17 +743,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Core 6</t>
+          <t>ServiceNow Instance 6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -783,17 +783,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HighRadius Core 7</t>
+          <t>Legacy AS/400 Core 7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -803,11 +803,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -823,35 +823,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tableau Core 8</t>
+          <t>HighRadius Core 8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -863,35 +863,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coupa Module 0</t>
+          <t>Tableau Core 0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.29</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -903,35 +903,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hyperion Instance 1</t>
+          <t>Coupa Module 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4.13</v>
+        <v>0.29</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -943,35 +943,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 2</t>
+          <t>Hyperion Instance 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -983,22 +983,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Salesforce Module 3</t>
+          <t>Custom .NET Instance 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coupa Module 4</t>
+          <t>Salesforce Module 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Power BI Instance 5</t>
+          <t>Coupa Module 5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1083,15 +1083,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3.28</v>
+        <v>1.11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1103,35 +1103,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Core 6</t>
+          <t>Power BI Instance 6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.79</v>
+        <v>3.28</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1143,22 +1143,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce Instance 7</t>
+          <t>Legacy AS/400 Core 7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1167,11 +1167,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3.97</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1183,22 +1183,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ServiceNow Instance 8</t>
+          <t>Salesforce Instance 8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.19</v>
+        <v>3.97</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1223,17 +1223,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Module 0</t>
+          <t>ServiceNow Instance 0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1243,15 +1243,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3.83</v>
+        <v>2.19</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1263,35 +1263,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Power BI Instance 1</t>
+          <t>Legacy AS/400 Module 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3.09</v>
+        <v>3.83</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1303,22 +1303,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAP ECC Module 2</t>
+          <t>Power BI Instance 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1327,11 +1327,11 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.3</v>
+        <v>3.09</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hyperion Instance 3</t>
+          <t>SAP ECC Module 3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1363,15 +1363,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.18</v>
+        <v>1.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1383,17 +1383,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 4</t>
+          <t>Hyperion Instance 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2.49</v>
+        <v>0.18</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1423,35 +1423,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Workday Instance 5</t>
+          <t>S/4HANA Instance 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.49</v>
+        <v>2.49</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hyperion Core 6</t>
+          <t>Workday Instance 6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1478,16 +1478,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1503,17 +1503,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HighRadius Instance 7</t>
+          <t>Hyperion Core 7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1523,11 +1523,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kyriba Instance 8</t>
+          <t>HighRadius Instance 8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1558,16 +1558,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.88</v>
+        <v>2.76</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1583,22 +1583,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyperion Instance 0</t>
+          <t>Kyriba Instance 0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.87</v>
+        <v>0.88</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1623,31 +1623,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Power BI Instance 1</t>
+          <t>Hyperion Instance 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.54</v>
+        <v>1.87</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1663,31 +1663,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blackline Module 2</t>
+          <t>Power BI Instance 2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1703,35 +1703,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Salesforce Instance 3</t>
+          <t>Blackline Module 3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3.21</v>
+        <v>0.96</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Core 4</t>
+          <t>Salesforce Instance 4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.17</v>
+        <v>3.21</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1783,35 +1783,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 5</t>
+          <t>Legacy AS/400 Core 5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3.34</v>
+        <v>2.17</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1823,35 +1823,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAP ECC Module 6</t>
+          <t>Custom .NET Instance 6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.93</v>
+        <v>3.34</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce Instance 7</t>
+          <t>SAP ECC Module 7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1878,20 +1878,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3.57</v>
+        <v>2.93</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tableau Core 8</t>
+          <t>Salesforce Instance 8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3.38</v>
+        <v>3.57</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Instance 0</t>
+          <t>Tableau Core 0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1963,15 +1963,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3.69</v>
+        <v>3.38</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1983,35 +1983,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 1</t>
+          <t>Legacy AS/400 Instance 1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2.1</v>
+        <v>3.69</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2023,35 +2023,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coupa Module 2</t>
+          <t>S/4HANA Instance 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Power BI Module 3</t>
+          <t>Coupa Module 3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,25 +2073,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2.57</v>
+        <v>1.33</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2103,31 +2103,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Core 4</t>
+          <t>Power BI Module 4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4.12</v>
+        <v>2.57</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2143,35 +2143,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hyperion Module 5</t>
+          <t>Legacy AS/400 Core 5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2188,30 +2188,30 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1.12</v>
+        <v>4.09</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2223,35 +2223,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salesforce Instance 7</t>
+          <t>Hyperion Module 7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.98</v>
+        <v>1.12</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HighRadius Instance 8</t>
+          <t>Salesforce Instance 8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2273,21 +2273,21 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2.47</v>
+        <v>0.98</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ServiceNow Core 0</t>
+          <t>HighRadius Instance 0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2318,20 +2318,20 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.64</v>
+        <v>2.47</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2343,35 +2343,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 1</t>
+          <t>ServiceNow Core 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2398,20 +2398,20 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.67</v>
+        <v>2.01</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2423,31 +2423,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Custom .NET Core 3</t>
+          <t>S/4HANA Instance 3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4.15</v>
+        <v>0.67</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2463,35 +2463,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Coupa Instance 4</t>
+          <t>Custom .NET Core 4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3.77</v>
+        <v>4.15</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2503,35 +2503,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kyriba Module 5</t>
+          <t>Coupa Instance 5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>3.06</v>
+        <v>3.77</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2543,17 +2543,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Coupa Module 6</t>
+          <t>Kyriba Module 6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2563,11 +2563,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2583,17 +2583,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Salesforce Module 7</t>
+          <t>Coupa Module 7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2603,11 +2603,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.79</v>
+        <v>2.88</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2623,35 +2623,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAP ECC Instance 8</t>
+          <t>Salesforce Module 8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.85</v>
+        <v>0.79</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2663,35 +2663,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tableau Instance 0</t>
+          <t>SAP ECC Instance 0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.9</v>
+        <v>1.85</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2703,35 +2703,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Legacy AS/400 Core 1</t>
+          <t>Tableau Instance 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4.07</v>
+        <v>0.9</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HighRadius Instance 2</t>
+          <t>Legacy AS/400 Core 2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2763,15 +2763,15 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.61</v>
+        <v>4.07</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2783,17 +2783,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Custom .NET Module 3</t>
+          <t>HighRadius Instance 3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2803,15 +2803,15 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>4.01</v>
+        <v>3.61</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ServiceNow Core 4</t>
+          <t>Custom .NET Module 4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2843,11 +2843,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.28</v>
+        <v>4.01</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ServiceNow Instance 5</t>
+          <t>ServiceNow Core 5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2873,25 +2873,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2.89</v>
+        <v>1.28</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2903,35 +2903,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salesforce Module 6</t>
+          <t>ServiceNow Instance 6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.48</v>
+        <v>2.89</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2943,35 +2943,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAP ECC Module 7</t>
+          <t>Salesforce Module 7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.21</v>
+        <v>1.48</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2983,17 +2983,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Custom .NET Core 8</t>
+          <t>SAP ECC Module 8</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3003,15 +3003,15 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3.77</v>
+        <v>0.21</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hyperion Core 0</t>
+          <t>Custom .NET Core 0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3043,15 +3043,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3063,35 +3063,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 1</t>
+          <t>Hyperion Core 1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Workday Module 2</t>
+          <t>Custom .NET Instance 2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3118,20 +3118,20 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Core 3</t>
+          <t>Workday Module 3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3163,15 +3163,15 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 4</t>
+          <t>Salesforce Core 4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3193,21 +3193,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3238,16 +3238,16 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>3.95</v>
+        <v>1.9</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Power BI Module 6</t>
+          <t>Custom .NET Instance 6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3278,20 +3278,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3303,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Workday Instance 7</t>
+          <t>Power BI Module 7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3327,11 +3327,11 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>4.08</v>
+        <v>1.02</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3343,35 +3343,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kyriba Core 8</t>
+          <t>Workday Instance 8</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.67</v>
+        <v>4.08</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3383,22 +3383,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ServiceNow Instance 0</t>
+          <t>Kyriba Core 0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3407,11 +3407,11 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2.97</v>
+        <v>0.67</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3428,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3447,11 +3447,11 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>4.18</v>
+        <v>2.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3463,35 +3463,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kyriba Core 2</t>
+          <t>ServiceNow Instance 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2.02</v>
+        <v>4.18</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3503,12 +3503,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kyriba Module 3</t>
+          <t>Kyriba Core 3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3518,20 +3518,20 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2.91</v>
+        <v>2.02</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Snowflake Instance 4</t>
+          <t>Kyriba Module 4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.55</v>
+        <v>2.91</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Snowflake Module 5</t>
+          <t>Snowflake Instance 5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3603,11 +3603,11 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>3.14</v>
+        <v>1.55</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3623,31 +3623,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAP ECC Module 6</t>
+          <t>Snowflake Module 6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3663,35 +3663,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hyperion Core 7</t>
+          <t>SAP ECC Module 7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3.42</v>
+        <v>2.81</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3703,31 +3703,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tableau Core 8</t>
+          <t>Hyperion Core 8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3743,35 +3743,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kyriba Module 0</t>
+          <t>Tableau Core 0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3783,31 +3783,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Coupa Instance 1</t>
+          <t>Kyriba Module 1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>3.01</v>
+        <v>3.17</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3823,22 +3823,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Snowflake Instance 2</t>
+          <t>Coupa Instance 2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3847,11 +3847,11 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>4.13</v>
+        <v>3.01</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3863,35 +3863,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Custom .NET Instance 3</t>
+          <t>Snowflake Instance 3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2.98</v>
+        <v>4.13</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tableau Module 4</t>
+          <t>Custom .NET Instance 4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3923,15 +3923,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>4.13</v>
+        <v>2.98</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3943,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ServiceNow Core 5</t>
+          <t>Tableau Module 5</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3958,20 +3958,20 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.06</v>
+        <v>4.13</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3983,35 +3983,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Coupa Module 6</t>
+          <t>ServiceNow Core 6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2.74</v>
+        <v>0.06</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4023,17 +4023,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Snowflake Core 7</t>
+          <t>Coupa Module 7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4043,11 +4043,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3.83</v>
+        <v>2.74</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4063,35 +4063,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Workday Module 8</t>
+          <t>Snowflake Core 8</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.16</v>
+        <v>3.83</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4103,35 +4103,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Coupa Instance 0</t>
+          <t>Workday Module 0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2.28</v>
+        <v>1.16</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4143,35 +4143,35 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S/4HANA Core 1</t>
+          <t>Coupa Instance 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Salesforce Module 2</t>
+          <t>S/4HANA Core 2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4193,25 +4193,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4223,35 +4223,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 3</t>
+          <t>Salesforce Module 3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>4.01</v>
+        <v>2.69</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kyriba Core 4</t>
+          <t>S/4HANA Instance 4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4278,20 +4278,20 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.15</v>
+        <v>4.01</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4303,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ServiceNow Core 5</t>
+          <t>Kyriba Core 5</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4318,16 +4318,16 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>3.22</v>
+        <v>1.15</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4343,35 +4343,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HighRadius Module 6</t>
+          <t>ServiceNow Core 6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1.42</v>
+        <v>3.22</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4383,35 +4383,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Snowflake Core 7</t>
+          <t>HighRadius Module 7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4423,35 +4423,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Snowflake Instance 8</t>
+          <t>Snowflake Core 8</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tableau Instance 0</t>
+          <t>Snowflake Instance 0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.2</v>
+        <v>2.63</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4503,35 +4503,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kyriba Module 1</t>
+          <t>Tableau Instance 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S/4HANA Core 2</t>
+          <t>Kyriba Module 2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4567,11 +4567,11 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3.06</v>
+        <v>0.52</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kyriba Instance 3</t>
+          <t>S/4HANA Core 3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4603,15 +4603,15 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.51</v>
+        <v>3.06</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Blackline Instance 4</t>
+          <t>Kyriba Instance 4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4638,20 +4638,20 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3.41</v>
+        <v>0.51</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -4663,17 +4663,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tableau Instance 5</t>
+          <t>Blackline Instance 5</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4687,11 +4687,11 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4703,35 +4703,35 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Salesforce Core 6</t>
+          <t>Tableau Instance 6</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tableau Instance 7</t>
+          <t>Salesforce Core 7</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4753,25 +4753,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3.89</v>
+        <v>1.95</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kyriba Core 8</t>
+          <t>Tableau Instance 8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4798,20 +4798,20 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.33</v>
+        <v>3.89</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -4823,35 +4823,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Power BI Instance 0</t>
+          <t>Kyriba Core 0</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>On-prem</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tableau Instance 1</t>
+          <t>Power BI Instance 1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4883,11 +4883,11 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3.61</v>
+        <v>1.86</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4903,17 +4903,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Salesforce Module 2</t>
+          <t>Tableau Instance 2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4943,35 +4943,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Blackline Core 3</t>
+          <t>Salesforce Module 3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>On-prem</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4983,35 +4983,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HighRadius Instance 4</t>
+          <t>Blackline Core 4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1.62</v>
+        <v>2.32</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Salesforce Instance 5</t>
+          <t>HighRadius Instance 5</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5043,15 +5043,15 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3.56</v>
+        <v>1.62</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5063,31 +5063,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S/4HANA Instance 6</t>
+          <t>Salesforce Instance 6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>PaaS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.83</v>
+        <v>3.56</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5103,35 +5103,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Workday Instance 7</t>
+          <t>S/4HANA Instance 7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5143,35 +5143,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SAP ECC Module 8</t>
+          <t>Workday Instance 8</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Migrate</t>
+          <t>Tolerate</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -5183,17 +5183,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Blackline Module 0</t>
+          <t>SAP ECC Module 0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Retire</t>
+          <t>Migrate</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5203,15 +5203,15 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2.22</v>
+        <v>1.09</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Snowflake Core 1</t>
+          <t>Blackline Module 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5233,21 +5233,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tolerate</t>
+          <t>Retire</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>3.86</v>
+        <v>2.22</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Snowflake Module 2</t>
+          <t>Snowflake Core 2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5278,20 +5278,20 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>IaaS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2.6</v>
+        <v>3.86</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
